--- a/TextGame project/Assets/Resources/Story/3.xlsx
+++ b/TextGame project/Assets/Resources/Story/3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hu137\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0FBE5F-4B58-417C-B716-988AD88307E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73D0CC1-6A69-4036-A646-AD0849974F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>旁白</t>
   </si>
@@ -120,10 +120,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>appearAt</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Qianye</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -147,7 +143,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>End of story</t>
+    <t>LastBGImg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastBGM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LastX2</t>
+  </si>
+  <si>
+    <t>LastX3</t>
+  </si>
+  <si>
+    <t>appearAtInstantly</t>
+  </si>
+  <si>
+    <t>goto</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -167,6 +184,7 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -508,17 +526,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
     <col min="7" max="7" width="10.44140625" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -570,13 +589,28 @@
       <c r="Q1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -585,98 +619,130 @@
         <v>4</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J2">
         <v>-640.83010000000002</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="T3">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <v>-640.83010000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:17">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:22">
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:22">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:22">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:22">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:22">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:22">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:22">
       <c r="B16" s="2"/>
     </row>
     <row r="17" spans="2:2">

--- a/TextGame project/Assets/Resources/Story/3.xlsx
+++ b/TextGame project/Assets/Resources/Story/3.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\share\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73D0CC1-6A69-4036-A646-AD0849974F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21942" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,98 +37,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="34">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>Vocal</t>
+  </si>
+  <si>
+    <t>BgImg</t>
+  </si>
+  <si>
+    <t>Bgm</t>
+  </si>
+  <si>
+    <t>PageAction</t>
+  </si>
+  <si>
+    <t>PageImage</t>
+  </si>
+  <si>
+    <t>Action1</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>Character1</t>
+  </si>
+  <si>
+    <t>Action2</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>Character2</t>
+  </si>
+  <si>
+    <t>Action3</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>Character3</t>
+  </si>
+  <si>
+    <t>LastBGImg</t>
+  </si>
+  <si>
+    <t>LastBGM</t>
+  </si>
+  <si>
+    <t>LastX1</t>
+  </si>
+  <si>
+    <t>LastX2</t>
+  </si>
+  <si>
+    <t>LastX3</t>
+  </si>
+  <si>
+    <t>千叶</t>
+  </si>
+  <si>
+    <t>还是算了吧... 太危险了，趁现在赶紧走！</t>
+  </si>
+  <si>
+    <t>Qianye</t>
+  </si>
+  <si>
+    <t>appearAtInstantly</t>
+  </si>
   <si>
     <t>旁白</t>
   </si>
   <si>
+    <t>（她转身往门口走，但走了几步又停了下来）</t>
+  </si>
+  <si>
     <t>White</t>
   </si>
   <si>
-    <t>千叶</t>
-  </si>
-  <si>
-    <t>Qianye</t>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dialogue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avatar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vocal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>BgImg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bgm</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PageAction</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PageImage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>x1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>x2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Action3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>x3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Character3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Qianye</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>还是算了吧... 太危险了，趁现在赶紧走！</t>
-  </si>
-  <si>
-    <t>（她转身往门口走，但走了几步又停了下来）</t>
-  </si>
-  <si>
     <t>可是... 那个男生一个人上去，会不会有危险啊？</t>
   </si>
   <si>
@@ -140,39 +136,22 @@
   </si>
   <si>
     <t>（她也往楼上走去）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastBGImg</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastBGM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LastX2</t>
-  </si>
-  <si>
-    <t>LastX3</t>
-  </si>
-  <si>
-    <t>appearAtInstantly</t>
   </si>
   <si>
     <t>goto</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,47 +163,354 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.8000000000000007"/>
+      <sz val="9.8"/>
       <color rgb="FFC9A26D"/>
       <name val="JetBrains Mono"/>
-      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -232,37 +518,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{EE10ED21-4A0F-409B-8ED9-0B3EC438B039}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -520,243 +1092,243 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="34.1083333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.4416666666667" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.3333333333333" customWidth="1"/>
+    <col min="11" max="11" width="11.6666666666667" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="R1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U1" t="s">
-        <v>31</v>
-      </c>
       <c r="V1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>33</v>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="R3">
         <v>4</v>
       </c>
       <c r="T3">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
       </c>
       <c r="R4">
         <v>4</v>
       </c>
       <c r="T4">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="R5">
         <v>4</v>
       </c>
       <c r="T5">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R6">
         <v>4</v>
       </c>
       <c r="T6">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="R7">
         <v>4</v>
       </c>
       <c r="T7">
-        <v>-640.83010000000002</v>
+        <v>-640.8301</v>
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:22">
-      <c r="B9" s="1"/>
+      <c r="B9" s="5"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="B10" s="1"/>
+      <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="B11" s="1"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="B12" s="1"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="B13" s="1"/>
+      <c r="B13" s="5"/>
     </row>
     <row r="14" spans="1:22">
-      <c r="B14" s="1"/>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" spans="1:22">
-      <c r="B15" s="1"/>
+      <c r="B15" s="5"/>
     </row>
     <row r="16" spans="1:22">
-      <c r="B16" s="2"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="1"/>
+      <c r="B17" s="5"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="1"/>
+      <c r="B18" s="5"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="2"/>
+      <c r="B19" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/TextGame project/Assets/Resources/Story/3.xlsx
+++ b/TextGame project/Assets/Resources/Story/3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1028AD2-DCDD-43E7-A44F-E7EFF0E291DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D55B1AD-1ABB-4F23-A096-0D94F6BE1326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -596,6 +596,9 @@
       <c r="E2">
         <v>4</v>
       </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
@@ -619,6 +622,9 @@
       <c r="R3">
         <v>4</v>
       </c>
+      <c r="S3">
+        <v>6</v>
+      </c>
       <c r="T3">
         <v>-640.83010000000002</v>
       </c>
@@ -636,6 +642,9 @@
       <c r="R4">
         <v>4</v>
       </c>
+      <c r="S4">
+        <v>6</v>
+      </c>
       <c r="T4">
         <v>-640.83010000000002</v>
       </c>
@@ -653,6 +662,9 @@
       <c r="R5">
         <v>4</v>
       </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
       <c r="T5">
         <v>-640.83010000000002</v>
       </c>
@@ -670,6 +682,9 @@
       <c r="R6">
         <v>4</v>
       </c>
+      <c r="S6">
+        <v>6</v>
+      </c>
       <c r="T6">
         <v>-640.83010000000002</v>
       </c>
@@ -686,6 +701,9 @@
       </c>
       <c r="R7">
         <v>4</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
       </c>
       <c r="T7">
         <v>-640.83010000000002</v>
